--- a/importer/live/standings/Player-Rankings-k946hMkXbiIfXMms8bKB.xlsx
+++ b/importer/live/standings/Player-Rankings-k946hMkXbiIfXMms8bKB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/E914DC20F5C50B12/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2297AE5F-836D-4287-99A6-DC653E3A4D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E13FA68-0459-4D1F-8A24-DA1072B76248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E7F8F387-838A-4492-B023-7DE3768D6816}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A4C4BED8-1B2B-4529-A6FD-7C2823D9450F}"/>
   </bookViews>
   <sheets>
     <sheet name="Player-Rankings-k946hMkXbiIfXMm" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
   <si>
     <t>Rank</t>
   </si>
@@ -52,61 +52,127 @@
     <t>Adam Beznicki</t>
   </si>
   <si>
+    <t>Peter Aglio</t>
+  </si>
+  <si>
+    <t>John Franzitta</t>
+  </si>
+  <si>
     <t>thomas page</t>
   </si>
   <si>
-    <t>John Franzitta</t>
-  </si>
-  <si>
     <t>Laura Pollicino</t>
   </si>
   <si>
     <t>LI-Kick</t>
   </si>
   <si>
+    <t>Danielle Farruggia</t>
+  </si>
+  <si>
+    <t>Daniel Glavin</t>
+  </si>
+  <si>
+    <t>BOX PICKLEBALL</t>
+  </si>
+  <si>
+    <t>Maurice Reilly</t>
+  </si>
+  <si>
+    <t>Joanna Sapir</t>
+  </si>
+  <si>
+    <t>Timothy Lynch</t>
+  </si>
+  <si>
+    <t>Billy Scaduto</t>
+  </si>
+  <si>
+    <t>Katie Prochilo</t>
+  </si>
+  <si>
+    <t>Jaime Frand</t>
+  </si>
+  <si>
+    <t>Andrew Heyman</t>
+  </si>
+  <si>
+    <t>Janeice Schmidt</t>
+  </si>
+  <si>
+    <t>Jaime Munch</t>
+  </si>
+  <si>
+    <t>Kenny Jee</t>
+  </si>
+  <si>
+    <t>Arthur Galo</t>
+  </si>
+  <si>
+    <t>1 Pickleball Plaza</t>
+  </si>
+  <si>
     <t>Dorothy Connolly</t>
   </si>
   <si>
+    <t>Shentah Pizarro</t>
+  </si>
+  <si>
+    <t>PxP PC</t>
+  </si>
+  <si>
+    <t>Adrian Lim</t>
+  </si>
+  <si>
+    <t>Ethan Miller</t>
+  </si>
+  <si>
+    <t>Daniel Wang</t>
+  </si>
+  <si>
     <t>Lisa Rogers</t>
   </si>
   <si>
-    <t>🇺🇸 Scadutes 🇺🇸</t>
-  </si>
-  <si>
-    <t>Chasette Gold</t>
+    <t>Sal Farruggia</t>
   </si>
   <si>
     <t>Christina Mazza</t>
   </si>
   <si>
-    <t>Peter Aglio</t>
-  </si>
-  <si>
-    <t>Tim D.</t>
-  </si>
-  <si>
-    <t>Karen P.</t>
+    <t>Kylie Lacerte</t>
+  </si>
+  <si>
+    <t>Peter Prochilo</t>
+  </si>
+  <si>
+    <t>Tim Duong</t>
+  </si>
+  <si>
+    <t>Karen Polito</t>
+  </si>
+  <si>
+    <t>Vincent Buonomo</t>
+  </si>
+  <si>
+    <t>Alexia Yaziciyan</t>
+  </si>
+  <si>
+    <t>Tom McDonough</t>
   </si>
   <si>
     <t>Frank Lao</t>
   </si>
   <si>
-    <t>BReady</t>
-  </si>
-  <si>
-    <t>Maurice Reilly</t>
-  </si>
-  <si>
-    <t>Jaime M.</t>
-  </si>
-  <si>
-    <t>Lani Licandro</t>
-  </si>
-  <si>
-    <t>Shentah Pizarro</t>
-  </si>
-  <si>
-    <t>PxP PC</t>
+    <t>Lorena Moncayo</t>
+  </si>
+  <si>
+    <t>Jarred Barretti</t>
+  </si>
+  <si>
+    <t>Elle Mac</t>
+  </si>
+  <si>
+    <t>Elena Licandro</t>
   </si>
   <si>
     <t>Gms</t>
@@ -127,19 +193,31 @@
     <t>Pts for</t>
   </si>
   <si>
-    <t xml:space="preserve">Pts aga </t>
+    <t>Pts aga</t>
   </si>
   <si>
     <t>Diff</t>
   </si>
   <si>
     <t>Gold</t>
+  </si>
+  <si>
+    <t>CARPENTERS PUB THURSDAY NIGHT</t>
+  </si>
+  <si>
+    <t>WEEK 5</t>
+  </si>
+  <si>
+    <t>MERRICK IN A PICKLE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -276,20 +354,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="ADLaM Display"/>
+      <name val="Dreaming Outloud Pro"/>
+      <family val="4"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Georgia Pro Cond Black"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,6 +549,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -657,7 +770,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -668,26 +781,57 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1063,408 +1207,384 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025C5410-1AC1-4736-8902-08E1BED781ED}">
-  <dimension ref="A1:P20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4C91A1-5770-41BA-879D-5EED1991DE9F}">
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:16" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+    </row>
+    <row r="2" spans="1:16" s="21" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="G2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="8">
-        <v>38</v>
-      </c>
-      <c r="E2" s="8">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1">
-        <v>6</v>
-      </c>
-      <c r="G2" s="8">
-        <v>22</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0.72699999999999998</v>
-      </c>
-      <c r="I2" s="1">
-        <v>2</v>
-      </c>
-      <c r="J2" s="8">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="8">
-        <f>D2/I2</f>
-        <v>19</v>
-      </c>
-      <c r="M2" s="1">
-        <v>240</v>
-      </c>
-      <c r="N2" s="1">
-        <v>217</v>
-      </c>
-      <c r="O2" s="8">
-        <v>23</v>
-      </c>
-      <c r="P2" s="8">
-        <v>1</v>
+      <c r="I2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="10">
-        <v>33</v>
-      </c>
-      <c r="E3" s="10">
-        <v>13</v>
+      <c r="D3" s="6">
+        <v>81</v>
+      </c>
+      <c r="E3" s="6">
+        <v>35</v>
       </c>
       <c r="F3" s="1">
-        <v>9</v>
-      </c>
-      <c r="G3" s="10">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.59099999999999997</v>
-      </c>
-      <c r="I3" s="1">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6">
+        <v>55</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="I3" s="6">
+        <v>5</v>
+      </c>
+      <c r="J3" s="6">
         <v>2</v>
       </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
       <c r="K3" s="1">
-        <v>2</v>
-      </c>
-      <c r="L3" s="1">
-        <f t="shared" ref="L3:L20" si="0">D3/I3</f>
-        <v>16.5</v>
-      </c>
-      <c r="M3" s="1">
-        <v>221</v>
+        <v>1</v>
+      </c>
+      <c r="L3" s="14">
+        <f>D3/I3</f>
+        <v>16.2</v>
+      </c>
+      <c r="M3" s="6">
+        <v>581</v>
       </c>
       <c r="N3" s="1">
-        <v>207</v>
-      </c>
-      <c r="O3" s="1">
-        <v>14</v>
-      </c>
-      <c r="P3" s="1"/>
+        <v>522</v>
+      </c>
+      <c r="O3" s="6">
+        <v>59</v>
+      </c>
+      <c r="P3" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1">
-        <v>26</v>
-      </c>
-      <c r="E4" s="1">
-        <v>11</v>
+      <c r="D4" s="6">
+        <v>81</v>
+      </c>
+      <c r="E4" s="10">
+        <v>34</v>
       </c>
       <c r="F4" s="1">
-        <v>11</v>
-      </c>
-      <c r="G4" s="8">
-        <v>22</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="1">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6">
+        <v>55</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="I4" s="6">
+        <v>5</v>
+      </c>
+      <c r="J4" s="6">
         <v>2</v>
       </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
       <c r="K4" s="1">
-        <v>4</v>
-      </c>
-      <c r="L4" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="M4" s="1">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L41" si="0">D4/I4</f>
+        <v>16.2</v>
+      </c>
+      <c r="M4" s="15">
+        <v>545</v>
       </c>
       <c r="N4" s="1">
-        <v>208</v>
-      </c>
-      <c r="O4" s="1">
-        <v>-8</v>
+        <v>500</v>
+      </c>
+      <c r="O4" s="13">
+        <v>45</v>
       </c>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1">
-        <v>10</v>
+      <c r="D5" s="9">
+        <v>58</v>
+      </c>
+      <c r="E5" s="9">
+        <v>26</v>
       </c>
       <c r="F5" s="1">
-        <v>12</v>
-      </c>
-      <c r="G5" s="8">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="G5" s="1">
+        <v>44</v>
       </c>
       <c r="H5" s="2">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="I5" s="13">
+        <v>4</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6</v>
-      </c>
-      <c r="L5" s="1">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>4</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
       </c>
       <c r="M5" s="1">
-        <v>218</v>
+        <v>441</v>
       </c>
       <c r="N5" s="1">
-        <v>221</v>
+        <v>408</v>
       </c>
       <c r="O5" s="1">
-        <v>-3</v>
+        <v>33</v>
       </c>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1">
+        <v>8</v>
+      </c>
+      <c r="D6" s="9">
+        <v>58</v>
+      </c>
+      <c r="E6" s="1">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1">
         <v>20</v>
       </c>
-      <c r="E6" s="1">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1">
-        <v>13</v>
-      </c>
-      <c r="G6" s="8">
-        <v>22</v>
+      <c r="G6" s="1">
+        <v>44</v>
       </c>
       <c r="H6" s="2">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="I6" s="13">
+        <v>4</v>
+      </c>
+      <c r="J6" s="13">
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>8</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
       </c>
       <c r="M6" s="1">
-        <v>209</v>
+        <v>445</v>
       </c>
       <c r="N6" s="1">
-        <v>217</v>
+        <v>404</v>
       </c>
       <c r="O6" s="1">
-        <v>-8</v>
-      </c>
-      <c r="P6" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="P6" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="E7" s="1">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>11</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="G7" s="6">
+        <v>55</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="6">
+        <v>5</v>
       </c>
       <c r="J7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="M7" s="1">
-        <v>121</v>
+        <v>4</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" si="0"/>
+        <v>11.4</v>
+      </c>
+      <c r="M7" s="9">
+        <v>492</v>
       </c>
       <c r="N7" s="1">
-        <v>87</v>
+        <v>539</v>
       </c>
       <c r="O7" s="1">
-        <v>34</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1</v>
-      </c>
+        <v>-47</v>
+      </c>
+      <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="I8" s="13">
+        <v>4</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1">
-        <v>16</v>
-      </c>
-      <c r="E8" s="1">
-        <v>6</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1">
-        <v>11</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>3</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
+      <c r="L8" s="4">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="M8" s="1">
-        <v>124</v>
+        <v>420</v>
       </c>
       <c r="N8" s="1">
-        <v>109</v>
+        <v>428</v>
       </c>
       <c r="O8" s="1">
-        <v>15</v>
+        <v>-8</v>
       </c>
       <c r="P8" s="1"/>
     </row>
@@ -1472,78 +1592,78 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>16</v>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1">
         <v>16</v>
       </c>
-      <c r="E9" s="1">
-        <v>6</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
+        <v>33</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
-        <v>11</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
+      <c r="L9" s="4">
+        <f t="shared" si="0"/>
+        <v>13.333333333333334</v>
       </c>
       <c r="M9" s="1">
-        <v>111</v>
+        <v>318</v>
       </c>
       <c r="N9" s="1">
-        <v>101</v>
+        <v>317</v>
       </c>
       <c r="O9" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D10" s="1">
+        <v>38</v>
+      </c>
+      <c r="E10" s="1">
         <v>14</v>
       </c>
-      <c r="E10" s="1">
-        <v>6</v>
-      </c>
       <c r="F10" s="1">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2">
-        <v>0.54500000000000004</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -1551,18 +1671,18 @@
       <c r="K10" s="1">
         <v>5</v>
       </c>
-      <c r="L10" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
+      <c r="L10" s="4">
+        <f t="shared" si="0"/>
+        <v>12.666666666666666</v>
       </c>
       <c r="M10" s="1">
-        <v>107</v>
+        <v>304</v>
       </c>
       <c r="N10" s="1">
-        <v>105</v>
+        <v>318</v>
       </c>
       <c r="O10" s="1">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="P10" s="1"/>
     </row>
@@ -1574,99 +1694,99 @@
         <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2">
-        <v>0.54500000000000004</v>
+        <v>0.441</v>
       </c>
       <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>5</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="L11" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="M11" s="1">
-        <v>111</v>
+        <v>325</v>
       </c>
       <c r="N11" s="1">
-        <v>108</v>
+        <v>331</v>
       </c>
       <c r="O11" s="1">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1">
         <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>11</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0.54500000000000004</v>
+        <v>23</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0.78300000000000003</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J12" s="13">
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>6</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="L12" s="8">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
       </c>
       <c r="M12" s="1">
-        <v>117</v>
+        <v>253</v>
       </c>
       <c r="N12" s="1">
-        <v>115</v>
-      </c>
-      <c r="O12" s="1">
-        <v>2</v>
+        <v>206</v>
+      </c>
+      <c r="O12" s="15">
+        <v>47</v>
       </c>
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>20</v>
@@ -1675,47 +1795,47 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H13" s="2">
-        <v>0.45500000000000002</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J13" s="13">
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>7</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
       </c>
       <c r="M13" s="1">
-        <v>113</v>
+        <v>217</v>
       </c>
       <c r="N13" s="1">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="O13" s="1">
-        <v>-1</v>
+        <v>31</v>
       </c>
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>21</v>
@@ -1724,41 +1844,41 @@
         <v>8</v>
       </c>
       <c r="D14" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2">
-        <v>0.45500000000000002</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="I14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>9</v>
-      </c>
-      <c r="L14" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="M14" s="1">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="N14" s="1">
-        <v>113</v>
+        <v>197</v>
       </c>
       <c r="O14" s="1">
-        <v>-5</v>
+        <v>19</v>
       </c>
       <c r="P14" s="1"/>
     </row>
@@ -1770,142 +1890,142 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2">
-        <v>0.45500000000000002</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="I15" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9</v>
-      </c>
-      <c r="L15" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="L15" s="4">
+        <f t="shared" si="0"/>
+        <v>9.6666666666666661</v>
       </c>
       <c r="M15" s="1">
-        <v>97</v>
+        <v>282</v>
       </c>
       <c r="N15" s="1">
-        <v>110</v>
+        <v>333</v>
       </c>
       <c r="O15" s="1">
-        <v>-13</v>
+        <v>-51</v>
       </c>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="1">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1">
-        <v>11</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0.45500000000000002</v>
+        <v>22</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.5</v>
       </c>
       <c r="I16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>10</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="L16" s="4">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
       </c>
       <c r="M16" s="1">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="N16" s="1">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O16" s="1">
-        <v>-5</v>
+        <v>17</v>
       </c>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E17" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H17" s="2">
         <v>0.27300000000000002</v>
       </c>
       <c r="I17" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>11</v>
-      </c>
-      <c r="L17" s="1">
+        <v>15</v>
+      </c>
+      <c r="L17" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="M17" s="1">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="N17" s="1">
-        <v>112</v>
+        <v>336</v>
       </c>
       <c r="O17" s="1">
-        <v>-16</v>
+        <v>-69</v>
       </c>
       <c r="P17" s="1"/>
     </row>
@@ -1913,148 +2033,1183 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G18" s="1">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H18" s="2">
-        <v>0.36399999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="I18" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>11</v>
-      </c>
-      <c r="L18" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="L18" s="4">
+        <f t="shared" si="0"/>
+        <v>7.666666666666667</v>
       </c>
       <c r="M18" s="1">
-        <v>110</v>
+        <v>254</v>
       </c>
       <c r="N18" s="1">
-        <v>118</v>
+        <v>365</v>
       </c>
       <c r="O18" s="1">
-        <v>-8</v>
+        <v>-111</v>
       </c>
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G19" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H19" s="2">
-        <v>0.36399999999999999</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="I19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>12</v>
-      </c>
-      <c r="L19" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="L19" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="M19" s="1">
-        <v>95</v>
+        <v>209</v>
       </c>
       <c r="N19" s="1">
-        <v>111</v>
+        <v>235</v>
       </c>
       <c r="O19" s="1">
-        <v>-16</v>
+        <v>-26</v>
       </c>
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
         <v>11</v>
       </c>
       <c r="H20" s="2">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="M20" s="1">
+        <v>117</v>
+      </c>
+      <c r="N20" s="1">
+        <v>79</v>
+      </c>
+      <c r="O20" s="1">
+        <v>38</v>
+      </c>
+      <c r="P20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1">
+        <v>11</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>11</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="M21" s="1">
+        <v>121</v>
+      </c>
+      <c r="N21" s="1">
+        <v>71</v>
+      </c>
+      <c r="O21" s="1">
+        <v>50</v>
+      </c>
+      <c r="P21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>17</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>11</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="M22" s="1">
+        <v>121</v>
+      </c>
+      <c r="N22" s="1">
+        <v>87</v>
+      </c>
+      <c r="O22" s="1">
+        <v>34</v>
+      </c>
+      <c r="P22" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="1">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1">
+        <v>15</v>
+      </c>
+      <c r="G23" s="1">
+        <v>23</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>12</v>
+      </c>
+      <c r="L23" s="4">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+      <c r="M23" s="1">
+        <v>206</v>
+      </c>
+      <c r="N23" s="1">
+        <v>242</v>
+      </c>
+      <c r="O23" s="1">
+        <v>-36</v>
+      </c>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1">
+        <v>11</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>2</v>
+      </c>
+      <c r="L24" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="M24" s="1">
+        <v>122</v>
+      </c>
+      <c r="N24" s="1">
+        <v>85</v>
+      </c>
+      <c r="O24" s="1">
+        <v>37</v>
+      </c>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="1">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>3</v>
+      </c>
+      <c r="L25" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="M25" s="1">
+        <v>127</v>
+      </c>
+      <c r="N25" s="1">
+        <v>99</v>
+      </c>
+      <c r="O25" s="1">
+        <v>28</v>
+      </c>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>11</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>4</v>
+      </c>
+      <c r="L26" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="M26" s="1">
+        <v>103</v>
+      </c>
+      <c r="N26" s="1">
+        <v>93</v>
+      </c>
+      <c r="O26" s="1">
+        <v>10</v>
+      </c>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1">
+        <v>6</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5</v>
+      </c>
+      <c r="G27" s="1">
+        <v>11</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>3</v>
+      </c>
+      <c r="L27" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="M27" s="1">
+        <v>124</v>
+      </c>
+      <c r="N27" s="1">
+        <v>109</v>
+      </c>
+      <c r="O27" s="1">
+        <v>15</v>
+      </c>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1">
+        <v>6</v>
+      </c>
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>11</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>6</v>
+      </c>
+      <c r="L28" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="M28" s="1">
+        <v>109</v>
+      </c>
+      <c r="N28" s="1">
+        <v>104</v>
+      </c>
+      <c r="O28" s="1">
+        <v>5</v>
+      </c>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5</v>
+      </c>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>5</v>
+      </c>
+      <c r="L29" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="M29" s="1">
+        <v>111</v>
+      </c>
+      <c r="N29" s="1">
+        <v>108</v>
+      </c>
+      <c r="O29" s="1">
+        <v>3</v>
+      </c>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="1">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1">
+        <v>6</v>
+      </c>
+      <c r="F30" s="1">
+        <v>6</v>
+      </c>
+      <c r="G30" s="1">
+        <v>12</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>10</v>
+      </c>
+      <c r="L30" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="M30" s="1">
+        <v>115</v>
+      </c>
+      <c r="N30" s="1">
+        <v>119</v>
+      </c>
+      <c r="O30" s="1">
+        <v>-4</v>
+      </c>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="1">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1">
+        <v>5</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5</v>
+      </c>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>9</v>
+      </c>
+      <c r="L31" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="M31" s="1">
+        <v>97</v>
+      </c>
+      <c r="N31" s="1">
+        <v>98</v>
+      </c>
+      <c r="O31" s="1">
+        <v>-1</v>
+      </c>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="1">
+        <v>12</v>
+      </c>
+      <c r="E32" s="1">
+        <v>5</v>
+      </c>
+      <c r="F32" s="1">
+        <v>6</v>
+      </c>
+      <c r="G32" s="1">
+        <v>11</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>7</v>
+      </c>
+      <c r="L32" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="M32" s="1">
+        <v>113</v>
+      </c>
+      <c r="N32" s="1">
+        <v>114</v>
+      </c>
+      <c r="O32" s="1">
+        <v>-1</v>
+      </c>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="1">
+        <v>10</v>
+      </c>
+      <c r="E33" s="1">
+        <v>5</v>
+      </c>
+      <c r="F33" s="1">
+        <v>6</v>
+      </c>
+      <c r="G33" s="1">
+        <v>11</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>9</v>
+      </c>
+      <c r="L33" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M33" s="1">
+        <v>108</v>
+      </c>
+      <c r="N33" s="1">
+        <v>113</v>
+      </c>
+      <c r="O33" s="1">
+        <v>-5</v>
+      </c>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="1">
+        <v>10</v>
+      </c>
+      <c r="E34" s="1">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1">
+        <v>7</v>
+      </c>
+      <c r="G34" s="1">
+        <v>11</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>13</v>
+      </c>
+      <c r="L34" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M34" s="1">
+        <v>94</v>
+      </c>
+      <c r="N34" s="1">
+        <v>115</v>
+      </c>
+      <c r="O34" s="1">
+        <v>-21</v>
+      </c>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1">
+        <v>11</v>
+      </c>
+      <c r="H35" s="2">
         <v>0.27300000000000002</v>
       </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="J20" s="1">
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
         <v>0</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K35" s="1">
+        <v>14</v>
+      </c>
+      <c r="L35" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M35" s="1">
+        <v>95</v>
+      </c>
+      <c r="N35" s="1">
+        <v>105</v>
+      </c>
+      <c r="O35" s="1">
+        <v>-10</v>
+      </c>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>31</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="1">
+        <v>10</v>
+      </c>
+      <c r="E36" s="1">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1">
+        <v>7</v>
+      </c>
+      <c r="G36" s="1">
+        <v>11</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>13</v>
+      </c>
+      <c r="L36" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M36" s="1">
+        <v>99</v>
+      </c>
+      <c r="N36" s="1">
+        <v>111</v>
+      </c>
+      <c r="O36" s="1">
+        <v>-12</v>
+      </c>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>31</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="1">
+        <v>10</v>
+      </c>
+      <c r="E37" s="1">
+        <v>5</v>
+      </c>
+      <c r="F37" s="1">
+        <v>6</v>
+      </c>
+      <c r="G37" s="1">
+        <v>11</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>9</v>
+      </c>
+      <c r="L37" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M37" s="1">
+        <v>97</v>
+      </c>
+      <c r="N37" s="1">
+        <v>110</v>
+      </c>
+      <c r="O37" s="1">
+        <v>-13</v>
+      </c>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="1">
+        <v>9</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1">
+        <v>8</v>
+      </c>
+      <c r="G38" s="1">
+        <v>11</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>16</v>
+      </c>
+      <c r="L38" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="M38" s="1">
+        <v>104</v>
+      </c>
+      <c r="N38" s="1">
+        <v>123</v>
+      </c>
+      <c r="O38" s="1">
+        <v>-19</v>
+      </c>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1">
+        <v>9</v>
+      </c>
+      <c r="E39" s="1">
+        <v>5</v>
+      </c>
+      <c r="F39" s="1">
+        <v>6</v>
+      </c>
+      <c r="G39" s="1">
+        <v>11</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>10</v>
+      </c>
+      <c r="L39" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="M39" s="1">
+        <v>103</v>
+      </c>
+      <c r="N39" s="1">
+        <v>108</v>
+      </c>
+      <c r="O39" s="1">
+        <v>-5</v>
+      </c>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>36</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1">
+        <v>9</v>
+      </c>
+      <c r="E40" s="1">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1">
+        <v>8</v>
+      </c>
+      <c r="G40" s="1">
         <v>12</v>
       </c>
-      <c r="L20" s="1">
-        <f t="shared" si="0"/>
+      <c r="H40" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>16</v>
+      </c>
+      <c r="L40" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="M40" s="1">
+        <v>88</v>
+      </c>
+      <c r="N40" s="1">
+        <v>126</v>
+      </c>
+      <c r="O40" s="1">
+        <v>-38</v>
+      </c>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="1">
         <v>7</v>
       </c>
-      <c r="M20" s="1">
-        <v>99</v>
-      </c>
-      <c r="N20" s="1">
-        <v>119</v>
-      </c>
-      <c r="O20" s="1">
-        <v>-20</v>
-      </c>
-      <c r="P20" s="1"/>
+      <c r="E41" s="1">
+        <v>4</v>
+      </c>
+      <c r="F41" s="1">
+        <v>7</v>
+      </c>
+      <c r="G41" s="1">
+        <v>11</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>12</v>
+      </c>
+      <c r="L41" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="M41" s="1">
+        <v>95</v>
+      </c>
+      <c r="N41" s="1">
+        <v>111</v>
+      </c>
+      <c r="O41" s="1">
+        <v>-16</v>
+      </c>
+      <c r="P41" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/importer/live/standings/Player-Rankings-k946hMkXbiIfXMms8bKB.xlsx
+++ b/importer/live/standings/Player-Rankings-k946hMkXbiIfXMms8bKB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/E914DC20F5C50B12/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E13FA68-0459-4D1F-8A24-DA1072B76248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C49D095C-89CB-47BB-BEFB-34951AA612DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A4C4BED8-1B2B-4529-A6FD-7C2823D9450F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{29D5D0D9-C684-4466-BD66-2AF9B0C81975}"/>
   </bookViews>
   <sheets>
     <sheet name="Player-Rankings-k946hMkXbiIfXMm" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
   <si>
     <t>Rank</t>
   </si>
@@ -43,15 +43,15 @@
     <t>Win %</t>
   </si>
   <si>
+    <t>Adam Beznicki</t>
+  </si>
+  <si>
+    <t>Merrick in a pickle</t>
+  </si>
+  <si>
     <t>Paul Heiser</t>
   </si>
   <si>
-    <t>Merrick in a pickle</t>
-  </si>
-  <si>
-    <t>Adam Beznicki</t>
-  </si>
-  <si>
     <t>Peter Aglio</t>
   </si>
   <si>
@@ -76,45 +76,51 @@
     <t>BOX PICKLEBALL</t>
   </si>
   <si>
+    <t>Timothy Lynch</t>
+  </si>
+  <si>
+    <t>Billy Scaduto</t>
+  </si>
+  <si>
+    <t>Arthur Galo</t>
+  </si>
+  <si>
+    <t>1 Pickleball Plaza</t>
+  </si>
+  <si>
+    <t>Katie Prochilo</t>
+  </si>
+  <si>
     <t>Maurice Reilly</t>
   </si>
   <si>
     <t>Joanna Sapir</t>
   </si>
   <si>
-    <t>Timothy Lynch</t>
-  </si>
-  <si>
-    <t>Billy Scaduto</t>
-  </si>
-  <si>
-    <t>Katie Prochilo</t>
+    <t>Janeice Schmidt</t>
+  </si>
+  <si>
+    <t>Andrew Heyman</t>
+  </si>
+  <si>
+    <t>Peter Prochilo</t>
   </si>
   <si>
     <t>Jaime Frand</t>
   </si>
   <si>
-    <t>Andrew Heyman</t>
-  </si>
-  <si>
-    <t>Janeice Schmidt</t>
-  </si>
-  <si>
     <t>Jaime Munch</t>
   </si>
   <si>
     <t>Kenny Jee</t>
   </si>
   <si>
-    <t>Arthur Galo</t>
-  </si>
-  <si>
-    <t>1 Pickleball Plaza</t>
-  </si>
-  <si>
     <t>Dorothy Connolly</t>
   </si>
   <si>
+    <t>Jarred Barretti</t>
+  </si>
+  <si>
     <t>Shentah Pizarro</t>
   </si>
   <si>
@@ -124,9 +130,15 @@
     <t>Adrian Lim</t>
   </si>
   <si>
+    <t>Lorena Moncayo</t>
+  </si>
+  <si>
     <t>Ethan Miller</t>
   </si>
   <si>
+    <t>Mikel Strauch</t>
+  </si>
+  <si>
     <t>Daniel Wang</t>
   </si>
   <si>
@@ -139,12 +151,12 @@
     <t>Christina Mazza</t>
   </si>
   <si>
+    <t>Jim Duffy</t>
+  </si>
+  <si>
     <t>Kylie Lacerte</t>
   </si>
   <si>
-    <t>Peter Prochilo</t>
-  </si>
-  <si>
     <t>Tim Duong</t>
   </si>
   <si>
@@ -163,12 +175,6 @@
     <t>Frank Lao</t>
   </si>
   <si>
-    <t>Lorena Moncayo</t>
-  </si>
-  <si>
-    <t>Jarred Barretti</t>
-  </si>
-  <si>
     <t>Elle Mac</t>
   </si>
   <si>
@@ -205,7 +211,7 @@
     <t>CARPENTERS PUB THURSDAY NIGHT</t>
   </si>
   <si>
-    <t>WEEK 5</t>
+    <t>WEEK 6</t>
   </si>
   <si>
     <t>MERRICK IN A PICKLE</t>
@@ -356,17 +362,17 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Dreaming Outloud Pro"/>
-      <family val="4"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="22"/>
       <color theme="1"/>
-      <name val="Georgia Pro Cond Black"/>
-      <family val="1"/>
+      <name val="ADLaM Display"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -554,13 +560,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,25 +578,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -770,7 +764,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -784,20 +778,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -806,33 +796,41 @@
     <xf numFmtId="10" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="39" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1207,216 +1205,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4C91A1-5770-41BA-879D-5EED1991DE9F}">
-  <dimension ref="A1:P41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B998EFD-A277-47F4-B6F3-69D439D5514A}">
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="5"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="20" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="1:16" s="21" customFormat="1" ht="30" x14ac:dyDescent="0.5">
+      <c r="A1" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+    </row>
+    <row r="2" spans="1:16" s="20" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16" t="s">
+      <c r="P2" s="22" t="s">
         <v>61</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-    </row>
-    <row r="2" spans="1:16" s="21" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="P2" s="18" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="6">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E3" s="6">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G3" s="6">
-        <v>55</v>
-      </c>
-      <c r="H3" s="11">
-        <v>0.63600000000000001</v>
+        <v>66</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.621</v>
       </c>
       <c r="I3" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>1</v>
-      </c>
-      <c r="L3" s="14">
+        <v>2</v>
+      </c>
+      <c r="L3" s="15">
         <f>D3/I3</f>
-        <v>16.2</v>
+        <v>16.333333333333332</v>
       </c>
       <c r="M3" s="6">
-        <v>581</v>
+        <v>661</v>
       </c>
       <c r="N3" s="1">
-        <v>522</v>
-      </c>
-      <c r="O3" s="6">
-        <v>59</v>
-      </c>
-      <c r="P3" s="6">
-        <v>1</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="O3" s="16">
+        <v>55</v>
+      </c>
+      <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="11">
         <v>81</v>
       </c>
-      <c r="E4" s="10">
-        <v>34</v>
+      <c r="E4" s="11">
+        <v>35</v>
       </c>
       <c r="F4" s="1">
-        <v>21</v>
-      </c>
-      <c r="G4" s="6">
+        <v>20</v>
+      </c>
+      <c r="G4" s="16">
         <v>55</v>
       </c>
-      <c r="H4" s="12">
-        <v>0.61799999999999999</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="H4" s="10">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="I4" s="11">
         <v>5</v>
       </c>
       <c r="J4" s="6">
         <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>2</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L41" si="0">D4/I4</f>
+        <v>1</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" ref="L4:L43" si="0">D4/I4</f>
         <v>16.2</v>
       </c>
-      <c r="M4" s="15">
-        <v>545</v>
+      <c r="M4" s="16">
+        <v>581</v>
       </c>
       <c r="N4" s="1">
-        <v>500</v>
-      </c>
-      <c r="O4" s="13">
-        <v>45</v>
-      </c>
-      <c r="P4" s="1"/>
+        <v>522</v>
+      </c>
+      <c r="O4" s="11">
+        <v>59</v>
+      </c>
+      <c r="P4" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="9">
-        <v>58</v>
-      </c>
-      <c r="E5" s="9">
-        <v>26</v>
+      <c r="D5" s="16">
+        <v>73</v>
+      </c>
+      <c r="E5" s="16">
+        <v>33</v>
       </c>
       <c r="F5" s="1">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1">
-        <v>44</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.59099999999999997</v>
-      </c>
-      <c r="I5" s="13">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="G5" s="16">
+        <v>55</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I5" s="11">
+        <v>5</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -1426,48 +1423,48 @@
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="M5" s="1">
-        <v>441</v>
+        <v>546</v>
       </c>
       <c r="N5" s="1">
-        <v>408</v>
+        <v>504</v>
       </c>
       <c r="O5" s="1">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="9">
-        <v>58</v>
+      <c r="D6" s="1">
+        <v>72</v>
       </c>
       <c r="E6" s="1">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1">
         <v>24</v>
       </c>
-      <c r="F6" s="1">
-        <v>20</v>
-      </c>
-      <c r="G6" s="1">
-        <v>44</v>
+      <c r="G6" s="16">
+        <v>55</v>
       </c>
       <c r="H6" s="2">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="I6" s="13">
-        <v>4</v>
-      </c>
-      <c r="J6" s="13">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="I6" s="11">
+        <v>5</v>
+      </c>
+      <c r="J6" s="19">
         <v>1</v>
       </c>
       <c r="K6" s="1">
@@ -1475,18 +1472,18 @@
       </c>
       <c r="L6" s="4">
         <f t="shared" si="0"/>
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="M6" s="1">
-        <v>445</v>
+        <v>555</v>
       </c>
       <c r="N6" s="1">
-        <v>404</v>
+        <v>506</v>
       </c>
       <c r="O6" s="1">
-        <v>41</v>
-      </c>
-      <c r="P6" s="6">
+        <v>49</v>
+      </c>
+      <c r="P6" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1494,29 +1491,29 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G7" s="6">
-        <v>55</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.4</v>
+        <v>66</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.379</v>
       </c>
       <c r="I7" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -1526,16 +1523,16 @@
       </c>
       <c r="L7" s="4">
         <f t="shared" si="0"/>
-        <v>11.4</v>
-      </c>
-      <c r="M7" s="9">
-        <v>492</v>
+        <v>11.166666666666666</v>
+      </c>
+      <c r="M7" s="11">
+        <v>601</v>
       </c>
       <c r="N7" s="1">
-        <v>539</v>
+        <v>664</v>
       </c>
       <c r="O7" s="1">
-        <v>-47</v>
+        <v>-63</v>
       </c>
       <c r="P7" s="1"/>
     </row>
@@ -1543,29 +1540,29 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="1">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1">
-        <v>24</v>
-      </c>
-      <c r="G8" s="1">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="G8" s="16">
+        <v>55</v>
       </c>
       <c r="H8" s="2">
         <v>0.45500000000000002</v>
       </c>
-      <c r="I8" s="13">
-        <v>4</v>
+      <c r="I8" s="11">
+        <v>5</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -1575,16 +1572,16 @@
       </c>
       <c r="L8" s="4">
         <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="M8" s="1">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="N8" s="1">
-        <v>428</v>
+        <v>523</v>
       </c>
       <c r="O8" s="1">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="P8" s="1"/>
     </row>
@@ -1592,29 +1589,29 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E9" s="1">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H9" s="2">
-        <v>0.51500000000000001</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="I9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1624,16 +1621,16 @@
       </c>
       <c r="L9" s="4">
         <f t="shared" si="0"/>
-        <v>13.333333333333334</v>
+        <v>14</v>
       </c>
       <c r="M9" s="1">
-        <v>318</v>
+        <v>428</v>
       </c>
       <c r="N9" s="1">
-        <v>317</v>
+        <v>418</v>
       </c>
       <c r="O9" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P9" s="1"/>
     </row>
@@ -1641,29 +1638,29 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="1">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2">
-        <v>0.42399999999999999</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="I10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -1673,16 +1670,16 @@
       </c>
       <c r="L10" s="4">
         <f t="shared" si="0"/>
-        <v>12.666666666666666</v>
+        <v>12.75</v>
       </c>
       <c r="M10" s="1">
-        <v>304</v>
+        <v>416</v>
       </c>
       <c r="N10" s="1">
-        <v>318</v>
+        <v>420</v>
       </c>
       <c r="O10" s="1">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="P10" s="1"/>
     </row>
@@ -1690,97 +1687,97 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="12" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E11" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2">
-        <v>0.441</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="I11" s="1">
         <v>3</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="1">
         <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="M11" s="1">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N11" s="1">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="O11" s="1">
-        <v>-6</v>
+        <v>32</v>
       </c>
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E12" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1">
-        <v>23</v>
-      </c>
-      <c r="H12" s="7">
-        <v>0.78300000000000003</v>
+        <v>32</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.59399999999999997</v>
       </c>
       <c r="I12" s="1">
-        <v>2</v>
-      </c>
-      <c r="J12" s="13">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1">
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>2</v>
-      </c>
-      <c r="L12" s="8">
-        <f t="shared" si="0"/>
-        <v>17.5</v>
+        <v>3</v>
+      </c>
+      <c r="L12" s="4">
+        <f t="shared" si="0"/>
+        <v>14.333333333333334</v>
       </c>
       <c r="M12" s="1">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="N12" s="1">
-        <v>206</v>
-      </c>
-      <c r="O12" s="15">
-        <v>47</v>
+        <v>295</v>
+      </c>
+      <c r="O12" s="1">
+        <v>28</v>
       </c>
       <c r="P12" s="1"/>
     </row>
@@ -1788,146 +1785,148 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D13" s="1">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E13" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
         <v>22</v>
       </c>
-      <c r="H13" s="2">
-        <v>0.63600000000000001</v>
+      <c r="H13" s="7">
+        <v>0.86399999999999999</v>
       </c>
       <c r="I13" s="1">
         <v>2</v>
       </c>
-      <c r="J13" s="13">
-        <v>1</v>
+      <c r="J13" s="6">
+        <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="L13" s="4">
-        <f t="shared" si="0"/>
-        <v>15.5</v>
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="M13" s="1">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="N13" s="1">
-        <v>186</v>
-      </c>
-      <c r="O13" s="1">
-        <v>31</v>
-      </c>
-      <c r="P13" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="O13" s="6">
+        <v>82</v>
+      </c>
+      <c r="P13" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>21</v>
+      <c r="B14" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E14" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1">
+        <v>31</v>
+      </c>
+      <c r="G14" s="1">
+        <v>45</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.311</v>
+      </c>
+      <c r="I14" s="1">
+        <v>4</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>11</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G14" s="1">
-        <v>22</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0.59099999999999997</v>
-      </c>
-      <c r="I14" s="1">
-        <v>2</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>3</v>
-      </c>
-      <c r="L14" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
       <c r="M14" s="1">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="N14" s="1">
-        <v>197</v>
+        <v>445</v>
       </c>
       <c r="O14" s="1">
-        <v>19</v>
+        <v>-91</v>
       </c>
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E15" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
         <v>34</v>
       </c>
       <c r="H15" s="2">
-        <v>0.35299999999999998</v>
+        <v>0.441</v>
       </c>
       <c r="I15" s="1">
         <v>3</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="0"/>
-        <v>9.6666666666666661</v>
+        <v>12</v>
       </c>
       <c r="M15" s="1">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="N15" s="1">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="O15" s="1">
-        <v>-51</v>
+        <v>-6</v>
       </c>
       <c r="P15" s="1"/>
     </row>
@@ -1935,48 +1934,48 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>35</v>
+      </c>
+      <c r="E16" s="1">
+        <v>18</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+      <c r="G16" s="1">
         <v>23</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="1">
-        <v>27</v>
-      </c>
-      <c r="E16" s="1">
-        <v>11</v>
-      </c>
-      <c r="F16" s="1">
-        <v>11</v>
-      </c>
-      <c r="G16" s="1">
-        <v>22</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.5</v>
+      <c r="H16" s="8">
+        <v>0.78300000000000003</v>
       </c>
       <c r="I16" s="1">
         <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>4</v>
-      </c>
-      <c r="L16" s="4">
-        <f t="shared" si="0"/>
-        <v>13.5</v>
+        <v>2</v>
+      </c>
+      <c r="L16" s="14">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
       </c>
       <c r="M16" s="1">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="N16" s="1">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="O16" s="1">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="P16" s="1"/>
     </row>
@@ -1984,254 +1983,250 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>24</v>
+      <c r="B17" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2">
-        <v>0.27300000000000002</v>
+        <v>0.182</v>
       </c>
       <c r="I17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="M17" s="1">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="N17" s="1">
-        <v>336</v>
+        <v>481</v>
       </c>
       <c r="O17" s="1">
-        <v>-69</v>
+        <v>-135</v>
       </c>
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E18" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G18" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H18" s="2">
-        <v>0.152</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="I18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="0"/>
-        <v>7.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="M18" s="1">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="N18" s="1">
-        <v>365</v>
+        <v>455</v>
       </c>
       <c r="O18" s="1">
-        <v>-111</v>
+        <v>-98</v>
       </c>
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E19" s="1">
+        <v>12</v>
+      </c>
+      <c r="F19" s="1">
         <v>9</v>
       </c>
-      <c r="F19" s="1">
-        <v>13</v>
-      </c>
       <c r="G19" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2">
-        <v>0.40899999999999997</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="I19" s="1">
         <v>2</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M19" s="1">
         <v>209</v>
       </c>
       <c r="N19" s="1">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="O19" s="1">
-        <v>-26</v>
+        <v>21</v>
       </c>
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>27</v>
+      </c>
+      <c r="E20" s="1">
+        <v>11</v>
+      </c>
+      <c r="F20" s="1">
+        <v>11</v>
+      </c>
+      <c r="G20" s="1">
+        <v>22</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>4</v>
+      </c>
+      <c r="L20" s="4">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="M20" s="1">
+        <v>204</v>
+      </c>
+      <c r="N20" s="1">
+        <v>187</v>
+      </c>
+      <c r="O20" s="1">
         <v>17</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="1">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1">
-        <v>9</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2</v>
-      </c>
-      <c r="G20" s="1">
-        <v>11</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1</v>
-      </c>
-      <c r="L20" s="4">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="M20" s="1">
-        <v>117</v>
-      </c>
-      <c r="N20" s="1">
-        <v>79</v>
-      </c>
-      <c r="O20" s="1">
-        <v>38</v>
-      </c>
-      <c r="P20" s="6">
-        <v>1</v>
-      </c>
+      <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D21" s="1">
         <v>20</v>
       </c>
       <c r="E21" s="1">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1">
+        <v>13</v>
+      </c>
+      <c r="G21" s="1">
+        <v>22</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
         <v>11</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>11</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1</v>
-      </c>
-      <c r="I21" s="1">
-        <v>1</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>1</v>
-      </c>
       <c r="L21" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M21" s="1">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="N21" s="1">
-        <v>71</v>
+        <v>235</v>
       </c>
       <c r="O21" s="1">
-        <v>50</v>
-      </c>
-      <c r="P21" s="6">
-        <v>1</v>
-      </c>
+        <v>-26</v>
+      </c>
+      <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -2251,7 +2246,7 @@
       <c r="G22" s="1">
         <v>11</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="9">
         <v>0.81799999999999995</v>
       </c>
       <c r="I22" s="1">
@@ -2268,73 +2263,75 @@
         <v>20</v>
       </c>
       <c r="M22" s="1">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N22" s="1">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="O22" s="1">
-        <v>34</v>
-      </c>
-      <c r="P22" s="6">
+        <v>38</v>
+      </c>
+      <c r="P22" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>23</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0.34799999999999998</v>
+        <v>11</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0.81799999999999995</v>
       </c>
       <c r="I23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="0"/>
-        <v>9.5</v>
+        <v>20</v>
       </c>
       <c r="M23" s="1">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c r="N23" s="1">
-        <v>242</v>
+        <v>87</v>
       </c>
       <c r="O23" s="1">
-        <v>-36</v>
-      </c>
-      <c r="P23" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>8</v>
@@ -2346,90 +2343,90 @@
         <v>9</v>
       </c>
       <c r="F24" s="1">
+        <v>12</v>
+      </c>
+      <c r="G24" s="1">
+        <v>21</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="I24" s="1">
         <v>2</v>
       </c>
-      <c r="G24" s="1">
-        <v>11</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
       <c r="J24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="M24" s="1">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="N24" s="1">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="O24" s="1">
-        <v>37</v>
+        <v>-10</v>
       </c>
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="1">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1">
+        <v>15</v>
+      </c>
+      <c r="G25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="1">
-        <v>18</v>
-      </c>
-      <c r="E25" s="1">
-        <v>9</v>
-      </c>
-      <c r="F25" s="1">
-        <v>3</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="H25" s="2">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
         <v>12</v>
       </c>
-      <c r="H25" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>3</v>
-      </c>
       <c r="L25" s="4">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>9.5</v>
       </c>
       <c r="M25" s="1">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="N25" s="1">
-        <v>99</v>
+        <v>242</v>
       </c>
       <c r="O25" s="1">
-        <v>28</v>
+        <v>-36</v>
       </c>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -2438,41 +2435,41 @@
         <v>8</v>
       </c>
       <c r="D26" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E26" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
         <v>11</v>
       </c>
       <c r="H26" s="2">
-        <v>0.72699999999999998</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
       </c>
       <c r="J26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M26" s="1">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="N26" s="1">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O26" s="1">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="P26" s="1"/>
     </row>
@@ -2487,139 +2484,139 @@
         <v>8</v>
       </c>
       <c r="D27" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
       <c r="F27" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G27" s="1">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H27" s="2">
-        <v>0.54500000000000004</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="I27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M27" s="1">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="N27" s="1">
-        <v>109</v>
+        <v>240</v>
       </c>
       <c r="O27" s="1">
-        <v>15</v>
+        <v>-39</v>
       </c>
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D28" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E28" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F28" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="1">
-        <v>11</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0.54500000000000004</v>
+        <v>12</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.75</v>
       </c>
       <c r="I28" s="1">
         <v>1</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M28" s="1">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="N28" s="1">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="O28" s="1">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E29" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
         <v>11</v>
       </c>
       <c r="H29" s="2">
-        <v>0.54500000000000004</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="J29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M29" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N29" s="1">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="O29" s="1">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="P29" s="1"/>
     </row>
@@ -2631,22 +2628,22 @@
         <v>39</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E30" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G30" s="1">
-        <v>12</v>
-      </c>
-      <c r="H30" s="3">
-        <v>0.5</v>
+        <v>11</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0.72699999999999998</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
@@ -2655,69 +2652,69 @@
         <v>0</v>
       </c>
       <c r="K30" s="1">
+        <v>4</v>
+      </c>
+      <c r="L30" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="M30" s="1">
+        <v>103</v>
+      </c>
+      <c r="N30" s="1">
+        <v>93</v>
+      </c>
+      <c r="O30" s="1">
         <v>10</v>
-      </c>
-      <c r="L30" s="4">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="M30" s="1">
-        <v>115</v>
-      </c>
-      <c r="N30" s="1">
-        <v>119</v>
-      </c>
-      <c r="O30" s="1">
-        <v>-4</v>
       </c>
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E31" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="1">
         <v>5</v>
       </c>
       <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="3">
-        <v>0.5</v>
+        <v>11</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.54500000000000004</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M31" s="1">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="N31" s="1">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="O31" s="1">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="P31" s="1"/>
     </row>
@@ -2732,19 +2729,19 @@
         <v>8</v>
       </c>
       <c r="D32" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1">
+        <v>6</v>
+      </c>
+      <c r="F32" s="1">
         <v>5</v>
-      </c>
-      <c r="F32" s="1">
-        <v>6</v>
       </c>
       <c r="G32" s="1">
         <v>11</v>
       </c>
       <c r="H32" s="2">
-        <v>0.45500000000000002</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -2753,20 +2750,20 @@
         <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M32" s="1">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N32" s="1">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="O32" s="1">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32" s="1"/>
     </row>
@@ -2778,22 +2775,22 @@
         <v>42</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D33" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E33" s="1">
+        <v>6</v>
+      </c>
+      <c r="F33" s="1">
         <v>5</v>
-      </c>
-      <c r="F33" s="1">
-        <v>6</v>
       </c>
       <c r="G33" s="1">
         <v>11</v>
       </c>
       <c r="H33" s="2">
-        <v>0.45500000000000002</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
@@ -2802,20 +2799,20 @@
         <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M33" s="1">
+        <v>111</v>
+      </c>
+      <c r="N33" s="1">
         <v>108</v>
       </c>
-      <c r="N33" s="1">
-        <v>113</v>
-      </c>
       <c r="O33" s="1">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="P33" s="1"/>
     </row>
@@ -2827,22 +2824,22 @@
         <v>43</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E34" s="1">
+        <v>7</v>
+      </c>
+      <c r="F34" s="1">
         <v>4</v>
-      </c>
-      <c r="F34" s="1">
-        <v>7</v>
       </c>
       <c r="G34" s="1">
         <v>11</v>
       </c>
       <c r="H34" s="2">
-        <v>0.36399999999999999</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
@@ -2851,26 +2848,26 @@
         <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L34" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M34" s="1">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="N34" s="1">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="O34" s="1">
-        <v>-21</v>
+        <v>7</v>
       </c>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>44</v>
@@ -2879,19 +2876,19 @@
         <v>14</v>
       </c>
       <c r="D35" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E35" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G35" s="1">
-        <v>11</v>
-      </c>
-      <c r="H35" s="2">
-        <v>0.27300000000000002</v>
+        <v>12</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0.5</v>
       </c>
       <c r="I35" s="1">
         <v>1</v>
@@ -2900,47 +2897,47 @@
         <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M35" s="1">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="N35" s="1">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="O35" s="1">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="P35" s="1"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1">
         <v>11</v>
       </c>
       <c r="H36" s="2">
-        <v>0.36399999999999999</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
@@ -2949,26 +2946,26 @@
         <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M36" s="1">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="N36" s="1">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O36" s="1">
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>46</v>
@@ -3005,40 +3002,40 @@
         <v>10</v>
       </c>
       <c r="M37" s="1">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="N37" s="1">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O37" s="1">
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D38" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1">
         <v>11</v>
       </c>
       <c r="H38" s="2">
-        <v>0.27300000000000002</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -3047,47 +3044,47 @@
         <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M38" s="1">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="N38" s="1">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="O38" s="1">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D39" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F39" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1">
         <v>11</v>
       </c>
       <c r="H39" s="2">
-        <v>0.45500000000000002</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -3096,47 +3093,47 @@
         <v>0</v>
       </c>
       <c r="K39" s="1">
+        <v>14</v>
+      </c>
+      <c r="L39" s="4">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L39" s="4">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
       <c r="M39" s="1">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="N39" s="1">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O39" s="1">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D40" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" s="1">
         <v>4</v>
       </c>
       <c r="F40" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G40" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H40" s="2">
-        <v>0.33300000000000002</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
@@ -3145,26 +3142,26 @@
         <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M40" s="1">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N40" s="1">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="O40" s="1">
-        <v>-38</v>
+        <v>-12</v>
       </c>
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>50</v>
@@ -3173,19 +3170,19 @@
         <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E41" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G41" s="1">
         <v>11</v>
       </c>
       <c r="H41" s="2">
-        <v>0.36399999999999999</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -3194,22 +3191,120 @@
         <v>0</v>
       </c>
       <c r="K41" s="1">
+        <v>9</v>
+      </c>
+      <c r="L41" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M41" s="1">
+        <v>97</v>
+      </c>
+      <c r="N41" s="1">
+        <v>110</v>
+      </c>
+      <c r="O41" s="1">
+        <v>-13</v>
+      </c>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="1">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4</v>
+      </c>
+      <c r="F42" s="1">
+        <v>8</v>
+      </c>
+      <c r="G42" s="1">
         <v>12</v>
       </c>
-      <c r="L41" s="4">
-        <f t="shared" si="0"/>
+      <c r="H42" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>16</v>
+      </c>
+      <c r="L42" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="M42" s="1">
+        <v>88</v>
+      </c>
+      <c r="N42" s="1">
+        <v>126</v>
+      </c>
+      <c r="O42" s="1">
+        <v>-38</v>
+      </c>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="1">
         <v>7</v>
       </c>
-      <c r="M41" s="1">
+      <c r="E43" s="1">
+        <v>4</v>
+      </c>
+      <c r="F43" s="1">
+        <v>7</v>
+      </c>
+      <c r="G43" s="1">
+        <v>11</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>12</v>
+      </c>
+      <c r="L43" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="M43" s="1">
         <v>95</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N43" s="1">
         <v>111</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O43" s="1">
         <v>-16</v>
       </c>
-      <c r="P41" s="1"/>
+      <c r="P43" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
